--- a/PRACTICA_EXCEL/practica excel.xlsx
+++ b/PRACTICA_EXCEL/practica excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Documents\oposCaib\PRACTICA_EXCEL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7775FE68-9082-4B8D-B704-153C97240CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC74B4F7-845A-4764-8202-E75437B1FAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6708640F-2A23-49F5-8BEC-A501D10050A3}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="gastos" sheetId="1" r:id="rId1"/>
     <sheet name="resumen" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gastos!$A$1:$D$32</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -30,12 +33,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="32">
   <si>
     <t>Fecha</t>
   </si>
@@ -115,16 +121,10 @@
     <t>DIVERSOS</t>
   </si>
   <si>
-    <t xml:space="preserve">NIÑOS </t>
-  </si>
-  <si>
     <t>ENTRETENIMIENTO</t>
   </si>
   <si>
     <t>ROPA</t>
-  </si>
-  <si>
-    <t>IMPUESTOS</t>
   </si>
   <si>
     <t>VIVIENDA</t>
@@ -387,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -422,6 +422,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -443,9 +445,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1212,6 +1211,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:D32" xr:uid="{531B1139-BCF6-490D-8BCC-589984E8BA34}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1225,24 +1225,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="19"/>
-      <c r="D1" s="20" t="s">
+      <c r="C1" s="21"/>
+      <c r="D1" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="F1" s="21" t="s">
+      <c r="E1" s="22"/>
+      <c r="F1" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="22"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="17"/>
+      <c r="A2" s="19"/>
       <c r="B2" s="6" t="s">
         <v>21</v>
       </c>
@@ -1267,12 +1267,12 @@
         <v>23</v>
       </c>
       <c r="B3" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A3,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A3)</f>
         <v>111</v>
       </c>
-      <c r="C3" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A3,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C3" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A3)</f>
+        <v>25</v>
       </c>
       <c r="D3" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A3,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1293,15 +1293,15 @@
     </row>
     <row r="4" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A4,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A4)</f>
         <v>55</v>
       </c>
-      <c r="C4" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A4,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C4" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A4)</f>
+        <v>25</v>
       </c>
       <c r="D4" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A4,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1325,12 +1325,12 @@
         <v>25</v>
       </c>
       <c r="B5" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A5,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A5)</f>
         <v>56</v>
       </c>
-      <c r="C5" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A5,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C5" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A5)</f>
+        <v>10</v>
       </c>
       <c r="D5" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A5,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1351,15 +1351,15 @@
     </row>
     <row r="6" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B6" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A6,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A6)</f>
         <v>44</v>
       </c>
-      <c r="C6" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A6,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C6" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A6)</f>
+        <v>22</v>
       </c>
       <c r="D6" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A6,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1379,45 +1379,45 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="14" t="s">
-        <v>29</v>
+      <c r="A7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="B7" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A7,gastos!$C$2:$C$32,$B$2)</f>
-        <v>0</v>
-      </c>
-      <c r="C7" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A7,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A7)</f>
+        <v>92</v>
+      </c>
+      <c r="C7" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A7)</f>
+        <v>114</v>
       </c>
       <c r="D7" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A7,gastos!$C$2:$C$32,resumen!D$2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A7,gastos!$C$2:$C$32,resumen!E$2)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="13" t="e">
+        <v>3</v>
+      </c>
+      <c r="F7" s="13">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A7,gastos!$C$2:$C$32,resumen!F$2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="13" t="e">
+        <v>46</v>
+      </c>
+      <c r="G7" s="13">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A7,gastos!$C$2:$C$32,resumen!G$2)</f>
-        <v>#DIV/0!</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B8" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A8,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A8)</f>
         <v>25</v>
       </c>
-      <c r="C8" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A8,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C8" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A8)</f>
+        <v>31</v>
       </c>
       <c r="D8" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A8,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1438,44 +1438,44 @@
     </row>
     <row r="9" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B9" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A9,gastos!$C$2:$C$32,$B$2)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A9,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A9)</f>
+        <v>34</v>
+      </c>
+      <c r="C9" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A9)</f>
+        <v>11</v>
       </c>
       <c r="D9" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A9,gastos!$C$2:$C$32,resumen!D$2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A9,gastos!$C$2:$C$32,resumen!E$2)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="13" t="e">
+        <v>1</v>
+      </c>
+      <c r="F9" s="13">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A9,gastos!$C$2:$C$32,resumen!F$2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="13" t="e">
+        <v>34</v>
+      </c>
+      <c r="G9" s="13">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A9,gastos!$C$2:$C$32,resumen!G$2)</f>
-        <v>#DIV/0!</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B10" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A10,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A10)</f>
         <v>71</v>
       </c>
-      <c r="C10" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A10,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C10" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A10)</f>
+        <v>5</v>
       </c>
       <c r="D10" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A10,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1499,12 +1499,12 @@
         <v>24</v>
       </c>
       <c r="B11" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A11,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A11)</f>
         <v>90</v>
       </c>
-      <c r="C11" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A11,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C11" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A11)</f>
+        <v>134</v>
       </c>
       <c r="D11" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A11,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1525,15 +1525,15 @@
     </row>
     <row r="12" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B12" s="12">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A12,gastos!$C$2:$C$32,$B$2)</f>
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A12)</f>
         <v>76</v>
       </c>
-      <c r="C12" s="12" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A12,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
+      <c r="C12" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A12)</f>
+        <v>84</v>
       </c>
       <c r="D12" s="11">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A12,gastos!$C$2:$C$32,resumen!D$2)</f>
@@ -1554,29 +1554,29 @@
     </row>
     <row r="13" spans="1:7" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" s="23">
-        <f>SUMIFS(gastos!$D$2:D$32,gastos!$B$2:$B$32,$A13,gastos!$C$2:$C$32,$B$2)</f>
+        <v>28</v>
+      </c>
+      <c r="B13" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!B$2,gastos!$B$2:$B$32,resumen!$A13)</f>
         <v>67</v>
       </c>
-      <c r="C13" s="23" t="e">
-        <f>SUMIFS(gastos!$D$2:E$32,gastos!$B$2:$B$32,$A13,gastos!$C$2:$C$32,$B$2)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="D13" s="24">
+      <c r="C13" s="12">
+        <f>SUMIFS(gastos!$D$2:$D$32,gastos!$C$2:$C$32,resumen!C$2,gastos!$B$2:$B$32,resumen!$A13)</f>
+        <v>11</v>
+      </c>
+      <c r="D13" s="16">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A13,gastos!$C$2:$C$32,resumen!D$2)</f>
         <v>2</v>
       </c>
-      <c r="E13" s="24">
+      <c r="E13" s="16">
         <f>COUNTIFS(gastos!$B$2:$B$32,resumen!$A13,gastos!$C$2:$C$32,resumen!E$2)</f>
         <v>1</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="17">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A13,gastos!$C$2:$C$32,resumen!F$2)</f>
         <v>33.5</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="17">
         <f>AVERAGEIFS(gastos!$D$2:$D$32,gastos!$B$2:$B$32,resumen!$A13,gastos!$C$2:$C$32,resumen!G$2)</f>
         <v>11</v>
       </c>
